--- a/quizzes/016_drug_suffixes_quiz--quizzes.xlsx
+++ b/quizzes/016_drug_suffixes_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1386,46 +1386,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ol</t>
+          <t>ul</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ol</t>
+          <t>ul</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ox</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ox</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ul</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ul</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1437,46 +1437,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>submission_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>submission_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1488,46 +1488,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>submission_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>submission_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1539,46 +1539,46 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1590,46 +1590,46 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1641,46 +1641,46 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1692,46 +1692,46 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1743,46 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
